--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487557_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487557_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.565</v>
+        <v>3.6603</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9513</v>
+        <v>8.805999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-5.3863</v>
+        <v>-5.1457</v>
       </c>
       <c r="G2" t="n">
         <v>7.6767</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7897</v>
+        <v>0.885</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3339</v>
+        <v>1.1886</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.5442</v>
+        <v>-0.3036</v>
       </c>
       <c r="V2" t="n">
         <v>-2.9429</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7985</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>5.6821</v>
+        <v>3.4901</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.8837</v>
+        <v>-3.4183</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1392</v>
@@ -688,13 +688,13 @@
         <v>1.3709</v>
       </c>
       <c r="S3" t="n">
-        <v>4.5222</v>
+        <v>1.7956</v>
       </c>
       <c r="T3" t="n">
-        <v>3.8252</v>
+        <v>1.6332</v>
       </c>
       <c r="U3" t="n">
-        <v>0.697</v>
+        <v>0.1623</v>
       </c>
       <c r="V3" t="n">
         <v>0.9823</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0667</v>
+        <v>-1.6749</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4818</v>
+        <v>-0.8321</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4151</v>
+        <v>-0.8428</v>
       </c>
       <c r="G4" t="n">
         <v>-1.1469</v>
@@ -766,13 +766,13 @@
         <v>0.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>3.0925</v>
+        <v>1.351</v>
       </c>
       <c r="T4" t="n">
-        <v>2.6984</v>
+        <v>1.3845</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3942</v>
+        <v>-0.0335</v>
       </c>
       <c r="V4" t="n">
         <v>0.2754</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.9637</v>
+        <v>-2.3249</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.7712</v>
+        <v>-1.7314</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1925</v>
+        <v>-0.5934</v>
       </c>
       <c r="G5" t="n">
         <v>-1.0558</v>
@@ -844,13 +844,13 @@
         <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.619</v>
+        <v>1.2579</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3276</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9466</v>
+        <v>0.5457</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1767</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CASADO MANCERAS</t>
+          <t>A. GARRIDO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.6422</v>
+        <v>-3.2396</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.6056</v>
+        <v>-1.2113</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0366</v>
+        <v>-2.0283</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2635</v>
+        <v>0.8164</v>
       </c>
       <c r="H6" t="n">
-        <v>0.045</v>
+        <v>0.8572</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.3085</v>
+        <v>-0.0408</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1927</v>
+        <v>3.481</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4491</v>
+        <v>1.7999</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6418</v>
+        <v>1.6811</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.0708</v>
+        <v>-2.6646</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4041</v>
+        <v>-0.9427</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6667</v>
+        <v>-1.7219</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.1543</v>
+        <v>-5.0921</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9377</v>
+        <v>-6.8547</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.949</v>
+        <v>0.6045</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4752</v>
+        <v>0.6705</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4738</v>
+        <v>-0.066</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.2754</v>
+        <v>0.4316</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2754</v>
+        <v>-1.0604</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. GONZALEZ MOTA</t>
+          <t>A. CASADO MANCERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.8311</v>
+        <v>-3.9199</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.5275</v>
+        <v>-2.8299</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.3036</v>
+        <v>-1.09</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1357</v>
+        <v>-1.2635</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3678</v>
+        <v>0.045</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7679</v>
+        <v>-1.3085</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9243</v>
+        <v>-0.1927</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2825</v>
+        <v>0.4491</v>
       </c>
       <c r="L7" t="n">
         <v>-0.6418</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2114</v>
+        <v>-1.0708</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0853</v>
+        <v>-0.4041</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1261</v>
+        <v>-0.6667</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.5253</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.917</v>
+        <v>-2.9377</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8183</v>
+        <v>-0.2267</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1782</v>
+        <v>0.3005</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6401</v>
+        <v>-0.5273</v>
       </c>
       <c r="V7" t="n">
-        <v>1.6482</v>
+        <v>-0.2754</v>
       </c>
       <c r="W7" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1562</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARRIDO RODRIGUEZ</t>
+          <t>S. GONZALEZ MOTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.6595</v>
+        <v>-4.266</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0698</v>
+        <v>-3.0158</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.5897</v>
+        <v>-1.2502</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8164</v>
+        <v>-2.1357</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8572</v>
+        <v>-1.3678</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0408</v>
+        <v>-0.7679</v>
       </c>
       <c r="J8" t="n">
-        <v>3.481</v>
+        <v>-0.9243</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7999</v>
+        <v>-0.2825</v>
       </c>
       <c r="L8" t="n">
-        <v>1.6811</v>
+        <v>-0.6418</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6646</v>
+        <v>-1.2114</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9427</v>
+        <v>-1.0853</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7219</v>
+        <v>-0.1261</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.0921</v>
+        <v>-3.5253</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.8547</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7626</v>
+        <v>0.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8154</v>
+        <v>-0.2532</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.188</v>
+        <v>0.3335</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6274</v>
+        <v>-0.5867</v>
       </c>
       <c r="V8" t="n">
-        <v>0.4316</v>
+        <v>1.6482</v>
       </c>
       <c r="W8" t="n">
         <v>1.492</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0604</v>
+        <v>0.1562</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-9.024699999999999</v>
+        <v>-8.4039</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.436</v>
+        <v>-2.3766</v>
       </c>
       <c r="F9" t="n">
-        <v>-6.5887</v>
+        <v>-6.0273</v>
       </c>
       <c r="G9" t="n">
         <v>-5.6845</v>
@@ -1156,13 +1156,13 @@
         <v>1.1751</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.2967</v>
       </c>
       <c r="T9" t="n">
-        <v>1.0369</v>
+        <v>1.0963</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3609</v>
+        <v>0.2004</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2742</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-20.691</v>
+        <v>-20.097</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2948999999999984</v>
+        <v>0.2989999999999995</v>
       </c>
       <c r="F10" t="n">
-        <v>-20.3962</v>
+        <v>-20.396</v>
       </c>
       <c r="G10" t="n">
         <v>-3.9325</v>
@@ -1234,13 +1234,13 @@
         <v>8.8131</v>
       </c>
       <c r="S10" t="n">
-        <v>6.116599999999998</v>
+        <v>6.710800000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>6.7254</v>
+        <v>7.3193</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6086</v>
+        <v>-0.6086999999999999</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3317</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>8.3276</v>
+        <v>8.968299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>6.8924</v>
+        <v>7.5064</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4352</v>
+        <v>1.4619</v>
       </c>
       <c r="G11" t="n">
         <v>4.8203</v>
@@ -1312,13 +1312,13 @@
         <v>3.1336</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.6678</v>
+        <v>-1.027</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0339</v>
+        <v>-0.4199</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6338</v>
+        <v>-0.6071</v>
       </c>
       <c r="V11" t="n">
         <v>2.4332</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.9502</v>
+        <v>5.6754</v>
       </c>
       <c r="E12" t="n">
-        <v>6.8014</v>
+        <v>4.9541</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1489</v>
+        <v>0.7213000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>1.3367</v>
+        <v>1.9359</v>
       </c>
       <c r="H12" t="n">
-        <v>1.4324</v>
+        <v>0.2889</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.09569999999999999</v>
+        <v>1.647</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6794</v>
+        <v>3.3494</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5177</v>
+        <v>1.8492</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1617</v>
+        <v>1.5002</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3427</v>
+        <v>-1.4135</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.0853</v>
+        <v>-1.5603</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.2573</v>
+        <v>0.1468</v>
       </c>
       <c r="P12" t="n">
-        <v>1.7626</v>
+        <v>3.1336</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7419</v>
+        <v>3.1336</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5179</v>
+        <v>-0.2777</v>
       </c>
       <c r="T12" t="n">
-        <v>3.8846</v>
+        <v>0.721</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3667</v>
+        <v>-0.9988</v>
       </c>
       <c r="V12" t="n">
-        <v>0.3329</v>
+        <v>0.8837</v>
       </c>
       <c r="W12" t="n">
-        <v>1.2166</v>
+        <v>0.8837</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.5697</v>
+        <v>5.3056</v>
       </c>
       <c r="E13" t="n">
-        <v>5.8751</v>
+        <v>5.3398</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6946</v>
+        <v>-0.0342</v>
       </c>
       <c r="G13" t="n">
-        <v>1.9359</v>
+        <v>3.9001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2889</v>
+        <v>-0.7629</v>
       </c>
       <c r="I13" t="n">
-        <v>1.647</v>
+        <v>4.6629</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3494</v>
+        <v>5.8562</v>
       </c>
       <c r="K13" t="n">
-        <v>1.8492</v>
+        <v>0.7995</v>
       </c>
       <c r="L13" t="n">
-        <v>1.5002</v>
+        <v>5.0567</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.4135</v>
+        <v>-1.9562</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5603</v>
+        <v>-1.5624</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1468</v>
+        <v>-0.3938</v>
       </c>
       <c r="P13" t="n">
-        <v>3.1336</v>
+        <v>2.9377</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R13" t="n">
         <v>3.1336</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6165</v>
+        <v>-0.6486</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6421</v>
+        <v>0.0123</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0255</v>
+        <v>-0.6609</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8837</v>
+        <v>-0.8837</v>
       </c>
       <c r="W13" t="n">
-        <v>0.8837</v>
+        <v>-0.3329</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.7137</v>
+        <v>4.8722</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8281</v>
+        <v>4.857</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1144</v>
+        <v>0.0152</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9001</v>
+        <v>1.3367</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.7629</v>
+        <v>1.4324</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6629</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8562</v>
+        <v>2.6794</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7995</v>
+        <v>2.5177</v>
       </c>
       <c r="L14" t="n">
-        <v>5.0567</v>
+        <v>0.1617</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.9562</v>
+        <v>-1.3427</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5624</v>
+        <v>-1.0853</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3938</v>
+        <v>-0.2573</v>
       </c>
       <c r="P14" t="n">
-        <v>2.9377</v>
+        <v>1.7626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.1958</v>
+        <v>-0.9792</v>
       </c>
       <c r="R14" t="n">
-        <v>3.1336</v>
+        <v>2.7419</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2404</v>
+        <v>1.4399</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4993</v>
+        <v>1.9403</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7411</v>
+        <v>-0.5004</v>
       </c>
       <c r="V14" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.2166</v>
+      </c>
+      <c r="X14" t="n">
         <v>-0.8837</v>
-      </c>
-      <c r="W14" t="n">
-        <v>-0.3329</v>
-      </c>
-      <c r="X14" t="n">
-        <v>-0.5507</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.7004</v>
+        <v>3.4553</v>
       </c>
       <c r="E15" t="n">
-        <v>2.2022</v>
+        <v>2.3045</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4982</v>
+        <v>1.1507</v>
       </c>
       <c r="G15" t="n">
         <v>-0.6539</v>
@@ -1624,13 +1624,13 @@
         <v>4.8962</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1424</v>
+        <v>-0.1028</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5023</v>
+        <v>0.6046</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3599</v>
+        <v>-0.7074</v>
       </c>
       <c r="V15" t="n">
         <v>1.2742</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4262</v>
+        <v>3.0669</v>
       </c>
       <c r="E16" t="n">
-        <v>3.1749</v>
+        <v>3.7889</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7487</v>
+        <v>-0.722</v>
       </c>
       <c r="G16" t="n">
         <v>0.9801</v>
@@ -1702,13 +1702,13 @@
         <v>3.3294</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7866</v>
+        <v>-1.1458</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8799</v>
+        <v>-0.2658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9067</v>
+        <v>-0.88</v>
       </c>
       <c r="V16" t="n">
         <v>1.2742</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4348</v>
+        <v>0.5417</v>
       </c>
       <c r="E17" t="n">
         <v>0.8045</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3697</v>
+        <v>-0.2628</v>
       </c>
       <c r="G17" t="n">
         <v>-0.06279999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>3.3294</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.1072</v>
+        <v>-2.0003</v>
       </c>
       <c r="T17" t="n">
         <v>-1.1704</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9368</v>
+        <v>-0.8299</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3329</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9913</v>
+        <v>-2.3727</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.9487</v>
+        <v>-2.4371</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0426</v>
+        <v>0.0643</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2931</v>
@@ -1858,13 +1858,13 @@
         <v>3.5253</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3238</v>
+        <v>-0.7052</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5234</v>
+        <v>-0.0118</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8003</v>
+        <v>-0.6934</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9412</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.6835</v>
+        <v>-4.0115</v>
       </c>
       <c r="E19" t="n">
-        <v>-4.5772</v>
+        <v>-4.0655</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1063</v>
+        <v>0.0541</v>
       </c>
       <c r="G19" t="n">
         <v>-4.0776</v>
@@ -1936,13 +1936,13 @@
         <v>1.9585</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3893</v>
+        <v>-0.7171999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7369</v>
+        <v>-0.2253</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6524</v>
+        <v>-0.492</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.7568</v>
+        <v>-4.8103</v>
       </c>
       <c r="E20" t="n">
         <v>-2.6567</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1001</v>
+        <v>-2.1536</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9532</v>
@@ -2014,13 +2014,13 @@
         <v>1.1751</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8784</v>
+        <v>-0.9319</v>
       </c>
       <c r="T20" t="n">
         <v>-0.5764</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3021</v>
+        <v>-0.3555</v>
       </c>
       <c r="V20" t="n">
         <v>-2.7086</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>20.691</v>
+        <v>20.69090000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>20.396</v>
+        <v>20.3959</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2951000000000001</v>
+        <v>0.2949000000000002</v>
       </c>
       <c r="G21" t="n">
         <v>3.9325</v>
@@ -2068,7 +2068,7 @@
         <v>18.3746</v>
       </c>
       <c r="K21" t="n">
-        <v>7.087999999999999</v>
+        <v>7.088000000000001</v>
       </c>
       <c r="L21" t="n">
         <v>11.2866</v>
@@ -2092,13 +2092,13 @@
         <v>30.3566</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.116699999999999</v>
+        <v>-6.1166</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6087999999999996</v>
+        <v>0.6085999999999996</v>
       </c>
       <c r="U21" t="n">
-        <v>-6.7253</v>
+        <v>-6.7254</v>
       </c>
       <c r="V21" t="n">
         <v>1.3318</v>
